--- a/backup/backup_Compte_Courant.xlsx
+++ b/backup/backup_Compte_Courant.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F167"/>
+  <dimension ref="A1:F171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,134 +465,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>45805</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Course </t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>APL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>120</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45803</v>
+        <v>45721</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>APL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>APL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>14.1</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45803</v>
+        <v>45782</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Virement</t>
+          <t>APL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banque </t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Livret_Bleu</t>
+          <t>APL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>300</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45803</v>
+        <v>45752</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Crous</t>
+          <t>APL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>APL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45802</v>
+        <v>45751</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Erreur de compte</t>
+          <t xml:space="preserve">Abonnement bar jeux de societe </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banque </t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Erreur de compte</t>
+          <t>Sortie</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -601,26 +599,26 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45801</v>
+        <v>45754</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">biere avec mathieux </t>
+          <t xml:space="preserve">Achat Pot et plante </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Reve</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alcool</t>
+          <t>Plante</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -629,26 +627,26 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>29.59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45801</v>
+        <v>45758</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>croissant</t>
+          <t xml:space="preserve">Achat Ticket Eileen </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Voyage</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Tram</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -657,26 +655,26 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45801</v>
+        <v>45741</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>spotify</t>
+          <t>Achat de coque, ecran ,baterie Lipo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Poisse</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Musique</t>
+          <t>Telephone</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -685,26 +683,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6.06</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45801</v>
+        <v>45712</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bonbon</t>
+          <t>Achat divers déménagement Action</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Demenagement</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -713,54 +711,54 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>20.33</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45801</v>
+        <v>45755</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Paye</t>
+          <t>Achat pour œuf a la coque</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Travail</t>
+          <t>Fourniture</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>659.76</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45801</v>
+        <v>45773</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>glace</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Fourniture</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -769,16 +767,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6.5</v>
+        <v>24.77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45801</v>
+        <v>45778</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>resto Mathieux bk</t>
+          <t xml:space="preserve">Addiction jeux d'argent </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -788,7 +786,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Addiction</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -797,16 +795,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>13.99</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45797</v>
+        <v>45748</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t xml:space="preserve">Addiction jeux d'argent </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -816,7 +814,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Addiction</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -825,16 +823,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45797</v>
+        <v>45717</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bar avec Emma</t>
+          <t>Alcool</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -853,26 +851,26 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45797</v>
+        <v>45774</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t xml:space="preserve">Anniv Laurianna </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Alcool</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -881,26 +879,26 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11.34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45797</v>
+        <v>45773</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Aquarium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Sortie</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -909,26 +907,26 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>26.45</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45794</v>
+        <v>45785</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Resto avec emma</t>
+          <t>Assurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t xml:space="preserve">Charge </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -937,26 +935,26 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>21</v>
+        <v>16.51</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45791</v>
+        <v>45726</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DLC cruisader King III</t>
+          <t>Assurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Jeux Vidéo</t>
+          <t xml:space="preserve">Charge </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -965,26 +963,26 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>43.99</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45791</v>
+        <v>45722</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Crous</t>
+          <t>Assurance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t xml:space="preserve">Charge </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -993,21 +991,21 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45789</v>
+        <v>45723</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bouffe</t>
+          <t>Bonbon pour allez mieux avec la prise de "Distance"</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1021,7 +1019,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>7.42</v>
+        <v>18.26</v>
       </c>
     </row>
     <row r="22">
@@ -1030,17 +1028,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cotisation</t>
+          <t>Bouffe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banque </t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cotisation</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1049,26 +1047,26 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.35</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45788</v>
+        <v>45706</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Plante</t>
+          <t>Cannette,Chocolat Chaud, Repas Semaines</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Reve</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Plante</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1077,26 +1075,26 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45786</v>
+        <v>45709</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>REPO</t>
+          <t>Caution</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Jeux Vidéo</t>
+          <t>Caution</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1105,82 +1103,82 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6.81</v>
+        <v>705</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45785</v>
+        <v>45706</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Assurance</t>
+          <t>Caution Parents</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>Habitation</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Charge </t>
-        </is>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>16.51</v>
+        <v>705</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45785</v>
+        <v>45697</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Train Dijon (Allez + 2 *Retour)</t>
+          <t>Compte au 09/02/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Voyage</t>
+          <t xml:space="preserve">Banque </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Solde du mois</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>55.5</v>
+        <v>484.42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45785</v>
+        <v>45789</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Electricite</t>
+          <t>Cotisation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t xml:space="preserve">Banque </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charge </t>
+          <t>Cotisation</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1189,26 +1187,26 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>80</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45782</v>
+        <v>45723</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Loyer</t>
+          <t xml:space="preserve">Cotisation </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t xml:space="preserve">Banque </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Loyer</t>
+          <t>Cotisation</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1217,63 +1215,63 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>705</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45782</v>
+        <v>45751</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Virement Papa</t>
+          <t xml:space="preserve">Cotisation </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t xml:space="preserve">Banque </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t>Cotisation</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>400</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45782</v>
+        <v>45797</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>APL</t>
+          <t>Course</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>196</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="31">
@@ -1282,17 +1280,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sortie avec Darius </t>
+          <t>Course</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sortie</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1301,16 +1299,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>12.84</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45780</v>
+        <v>45797</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fourniture en tout genre (PC + rideau)</t>
+          <t>Course</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1320,7 +1318,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fourniture</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1329,16 +1327,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>21.36</v>
+        <v>26.45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45780</v>
+        <v>45805</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t xml:space="preserve">Course </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1357,26 +1355,26 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>9.06</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45780</v>
+        <v>45738</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>achat ordinateur a darius</t>
+          <t>Course Loisir</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poisse</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ordinateur</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1385,44 +1383,44 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>257.9</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45778</v>
+        <v>45763</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Virement Maman</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>400</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45778</v>
+        <v>45797</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Resto Lucas-Charly</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1441,49 +1439,49 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45778</v>
+        <v>45765</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Remboursement train dijon</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>70</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45778</v>
+        <v>45803</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Resto Lucas - Charly</t>
+          <t>Crous</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1497,26 +1495,26 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45778</v>
+        <v>45733</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addiction jeux d'argent </t>
+          <t>Crous</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Addiction</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1525,26 +1523,26 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45777</v>
+        <v>45731</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Train Dijon</t>
+          <t>Crous</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Voyage</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1553,26 +1551,26 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>15.8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45774</v>
+        <v>45791</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anniv Laurianna </t>
+          <t>Crous</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Alcool</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1581,26 +1579,26 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45773</v>
+        <v>45762</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Aquarium</t>
+          <t>Crous</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sortie</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1609,16 +1607,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45773</v>
+        <v>45726</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Crous</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1628,7 +1626,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fourniture</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1637,16 +1635,16 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>24.77</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45773</v>
+        <v>45756</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Crous</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1665,54 +1663,54 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>104.2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45772</v>
+        <v>45771</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Paye</t>
+          <t>Crous</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Travail</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>659.76</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45771</v>
+        <v>45791</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deplacement Sainte</t>
+          <t>DLC cruisader King III</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Voyage</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Jeux Vidéo</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1721,7 +1719,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>30</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="47">
@@ -1730,17 +1728,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Crous</t>
+          <t>Deplacement Sainte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Voyage</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1749,54 +1747,54 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45770</v>
+        <v>45703</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fiver</t>
+          <t>Déplacement Lyon Appartement</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banque </t>
+          <t>Voyage</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Travail</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>53.4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45769</v>
+        <v>45698</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Eau</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Musique</t>
+          <t xml:space="preserve">Charge </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1805,26 +1803,26 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6.99</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45769</v>
+        <v>45755</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rose soiree lau et guigui</t>
+          <t>Electricite</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Alcool</t>
+          <t xml:space="preserve">Charge </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1833,26 +1831,26 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>14.35</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45767</v>
+        <v>45785</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Erreur JLC</t>
+          <t>Electricite</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fourniture</t>
+          <t xml:space="preserve">Charge </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1861,7 +1859,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>12.63</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52">
@@ -1894,39 +1892,39 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45765</v>
+        <v>45747</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>feria lyon avec lau et guiguui</t>
+          <t>Equilibrage du compte courant</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Alcool</t>
+          <t>Erreur de compte</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>38</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45765</v>
+        <v>45738</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Equipement Piscine</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1936,7 +1934,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1945,16 +1943,16 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>4.7</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45765</v>
+        <v>45767</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Resto avec Emma</t>
+          <t>Erreur JLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1964,7 +1962,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Fourniture</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1973,26 +1971,26 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>11</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45764</v>
+        <v>45712</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Virement</t>
+          <t>Erreur de Compte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banque </t>
+          <t>Erreur de compte</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Livret_Bleu</t>
+          <t>Erreur de compte</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2001,26 +1999,26 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
+        <v>124.91</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45763</v>
+        <v>45802</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Match Rugby</t>
+          <t>Erreur de compte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t xml:space="preserve">Banque </t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Erreur de compte</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2029,26 +2027,26 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45763</v>
+        <v>45711</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Essence</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Voyage</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2057,54 +2055,54 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3.9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45763</v>
+        <v>45733</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Frost Punk DLC + FrostPunk</t>
+          <t>Etude Inspire</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Jeux Vidéo</t>
+          <t>Travail</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>32</v>
+        <v>400</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45762</v>
+        <v>45710</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Crous</t>
+          <t>Exeptionnel Tram</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Voyage</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Tram</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2113,72 +2111,72 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>20</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45761</v>
+        <v>45770</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Resto</t>
+          <t>Fiver</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t xml:space="preserve">Banque </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Travail</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>9.9</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45758</v>
+        <v>45698</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Achat Ticket Eileen </t>
+          <t>Fiver</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Voyage</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tram</t>
+          <t>Travail</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>7.1</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45757</v>
+        <v>45780</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>pain</t>
+          <t>Fourniture en tout genre (PC + rideau)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2188,7 +2186,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Fourniture</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2197,26 +2195,26 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>7.5</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45756</v>
+        <v>45763</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Crous</t>
+          <t>Frost Punk DLC + FrostPunk</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Jeux Vidéo</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2225,44 +2223,44 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45755</v>
+        <v>45747</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Macdo Avec Emma</t>
+          <t>Gain Fiver</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Fiver</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>15.3</v>
+        <v>32.51</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45755</v>
+        <v>45752</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Electricite</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2281,26 +2279,26 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>80</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45755</v>
+        <v>45727</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Achat pour œuf a la coque</t>
+          <t>Jeux pour eileen</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fourniture</t>
+          <t>Jeux Vidéo</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2309,26 +2307,26 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>4.1</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45754</v>
+        <v>45735</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Achat Pot et plante </t>
+          <t>Kinder Bueno</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Reve</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Plante</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2337,26 +2335,26 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>29.59</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45754</v>
+        <v>45734</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nouveau Manteux</t>
+          <t>Kinder Bueno</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fourniture</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2365,26 +2363,26 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>39.99</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45754</v>
+        <v>45721</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Loyer</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Loyer</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2393,68 +2391,68 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>77.20999999999999</v>
+        <v>705</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45752</v>
+        <v>45698</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Virement Papa</t>
+          <t>Loyer</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t>Loyer</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>400</v>
+        <v>229</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45752</v>
+        <v>45711</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>APL</t>
+          <t>Loyer</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>APL</t>
+          <t>Loyer</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>196</v>
+        <v>137</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45752</v>
+        <v>45782</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2486,17 +2484,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>Loyer</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
           <t>Habitation</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Habitation</t>
-        </is>
-      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charge </t>
+          <t>Loyer</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2505,26 +2503,26 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>13.3</v>
+        <v>705</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45751</v>
+        <v>45813</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abonnement bar jeux de societe </t>
+          <t>Loyer</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sortie</t>
+          <t>Loyer</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2533,26 +2531,26 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>10</v>
+        <v>705</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45751</v>
+        <v>45755</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cotisation </t>
+          <t>Macdo Avec Emma</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banque </t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cotisation</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2561,26 +2559,26 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3.35</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45748</v>
+        <v>45727</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TCL</t>
+          <t>Match Rugby</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Voyage</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tram</t>
+          <t>Match</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2589,54 +2587,54 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45748</v>
+        <v>45763</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Virement Maman</t>
+          <t>Match Rugby</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t>Match</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>400</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45748</v>
+        <v>45715</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addiction jeux d'argent </t>
+          <t>Medoc pour tatouage</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Reve</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Addiction</t>
+          <t>Tatouage</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2645,35 +2643,35 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>25</v>
+        <v>70.73</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45747</v>
+        <v>45728</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gain Fiver</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Fiver</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>32.51</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="81">
@@ -2682,31 +2680,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Equilibrage du compte courant</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Erreur de compte</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>140</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45747</v>
+        <v>45719</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -2729,26 +2727,26 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>39.1</v>
+        <v>43.16</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45747</v>
+        <v>45707</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Terreau +…</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Reve</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Plante</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2757,26 +2755,26 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>10.29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45745</v>
+        <v>45754</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Plante</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banque </t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Livret_Bleu</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2785,26 +2783,26 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>84</v>
+        <v>77.20999999999999</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45745</v>
+        <v>45741</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Plante</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Reve</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Plante</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2813,12 +2811,12 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>80</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45741</v>
+        <v>45773</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -2841,26 +2839,26 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>13.16</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45741</v>
+        <v>45726</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Virement</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banque </t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Livret_Bleu</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2869,26 +2867,26 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>200</v>
+        <v>18.47</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45741</v>
+        <v>45722</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Achat de coque, ecran ,baterie Lipo</t>
+          <t>NourritureMidi</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poisse</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Telephone</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2897,21 +2895,21 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>70</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45741</v>
+        <v>45718</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nourritureavec Lauriana et guigui</t>
+          <t>NourritureMidi</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2925,26 +2923,26 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>28</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45741</v>
+        <v>45719</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Rachat téléphone après racket</t>
+          <t>NourritureMidi</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poisse</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Telephone</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2953,82 +2951,82 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>159</v>
+        <v>17.66</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45740</v>
+        <v>45741</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Virement</t>
+          <t>Nourritureavec Lauriana et guigui</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banque </t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Livret_Bleu</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45740</v>
+        <v>45724</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Paye</t>
+          <t>Nourrituresemaine</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Travail</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>659.76</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45740</v>
+        <v>45714</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ternardier Project</t>
+          <t xml:space="preserve">Nourrituresoir arrivé lyon </t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Reve</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Reve</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3037,26 +3035,26 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>70</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45738</v>
+        <v>45754</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Equipement Piscine</t>
+          <t>Nouveau Manteux</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Fourniture</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3065,21 +3063,21 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>4.59</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45738</v>
+        <v>45724</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Course Loisir</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3093,16 +3091,16 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>21.6</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45736</v>
+        <v>45718</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>pain</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3121,26 +3119,26 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>6.55</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45735</v>
+        <v>45712</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kinder Bueno</t>
+          <t>Parking Sainté</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Voyage</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3149,138 +3147,138 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45734</v>
+        <v>45801</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Kinder Bueno</t>
+          <t>Paye</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Travail</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1.6</v>
+        <v>659.76</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45733</v>
+        <v>45740</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Virement</t>
+          <t>Paye</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banque </t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Livret_Bleu</t>
+          <t>Travail</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>350</v>
+        <v>659.76</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45733</v>
+        <v>45772</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Crous</t>
+          <t>Paye</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Travail</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>40</v>
+        <v>659.76</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45733</v>
+        <v>45745</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Etude Inspire</t>
+          <t>Plante</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t xml:space="preserve">Banque </t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Travail</t>
+          <t>Livret_Bleu</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>400</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45732</v>
+        <v>45745</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Resto sortie dehors</t>
+          <t>Plante</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Reve</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Plante</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3289,26 +3287,26 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>10.9</v>
+        <v>80</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45731</v>
+        <v>45788</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>fourniture en tout genre</t>
+          <t>Plante</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Reve</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Fourniture</t>
+          <t>Plante</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3317,26 +3315,26 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>48.27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45731</v>
+        <v>45786</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Crous</t>
+          <t>REPO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Jeux Vidéo</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3345,110 +3343,110 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>10</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45730</v>
+        <v>45741</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Virement</t>
+          <t>Rachat téléphone après racket</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banque </t>
+          <t>Poisse</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Livret_Bleu</t>
+          <t>Telephone</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>100</v>
+        <v>159</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45730</v>
+        <v>45712</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Resto avec Emma</t>
+          <t>Remboursement Pneu et Baterie</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Poisse</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>9.9</v>
+        <v>246</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45729</v>
+        <v>45778</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>fourniture en tout genre</t>
+          <t>Remboursement train dijon</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Fourniture</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1.1</v>
+        <v>70</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45728</v>
+        <v>45711</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Remplacement Pneu et baterie</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Poisse</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Voiture</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3457,26 +3455,26 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>11.25</v>
+        <v>266</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45727</v>
+        <v>45703</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Jeux pour eileen</t>
+          <t>Repas resto le midi et recherche appartement</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Jeux Vidéo</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3485,16 +3483,16 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>9.75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45727</v>
+        <v>45713</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Match Rugby</t>
+          <t>Restaurant Mathieux</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3504,7 +3502,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3513,21 +3511,21 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45726</v>
+        <v>45761</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Crous</t>
+          <t>Resto</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3541,21 +3539,21 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>20</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>45726</v>
+        <v>45778</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Resto Lucas - Charly</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3569,26 +3567,26 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>18.47</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>45726</v>
+        <v>45778</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Assurance</t>
+          <t>Resto Lucas-Charly</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charge </t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3597,26 +3595,26 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>45725</v>
+        <v>45765</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tram Charly</t>
+          <t>Resto avec Emma</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Voyage</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Tram</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -3625,21 +3623,21 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>45724</v>
+        <v>45715</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nourrituresemaine</t>
+          <t>Resto avec Emma</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3653,21 +3651,21 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>52.65</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>45724</v>
+        <v>45730</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Resto avec Emma</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3681,26 +3679,26 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>2.97</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>45724</v>
+        <v>45794</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>fourniture en tout genre</t>
+          <t>Resto avec emma</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Fourniture</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3709,16 +3707,16 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>19.96</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>45723</v>
+        <v>45732</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bonbon pour allez mieux avec la prise de "Distance"</t>
+          <t>Resto sortie dehors</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3737,26 +3735,26 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>18.26</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>45723</v>
+        <v>45702</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cotisation </t>
+          <t>Restorant Margaux Titouan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banque </t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Cotisation</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3765,54 +3763,54 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>3.35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>45722</v>
+        <v>45709</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t xml:space="preserve">Restorant avec les P&amp;T guys </t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Musique</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>6.99</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>45722</v>
+        <v>45769</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NourritureMidi</t>
+          <t>Rose soiree lau et guigui</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Alcool</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3821,16 +3819,16 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>5.5</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>45722</v>
+        <v>45713</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Soggy</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3840,7 +3838,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Musique</t>
+          <t>Alcool</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3849,26 +3847,26 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>6.99</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>45722</v>
+        <v>45710</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Assurance</t>
+          <t>Soggy</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charge </t>
+          <t>Alcool</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -3877,26 +3875,26 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>11.56</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>45721</v>
+        <v>45780</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Loyer</t>
+          <t xml:space="preserve">Sortie avec Darius </t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Loyer</t>
+          <t>Sortie</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3905,82 +3903,82 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>705</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>APL</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>APL</t>
+          <t>Musique</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>196</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>45719</v>
+        <v>45722</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Tram</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Voyage</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tram</t>
+          <t>Musique</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>14</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>45719</v>
+        <v>45769</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Musique</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -3989,26 +3987,26 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>43.16</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>45719</v>
+        <v>45698</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NourritureMidi</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Musique</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4017,26 +4015,26 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>17.66</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>45718</v>
+        <v>45748</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>TCL</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Voyage</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Tram</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4045,26 +4043,26 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2.05</v>
+        <v>25</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>45718</v>
+        <v>45714</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NourritureMidi</t>
+          <t>Tatouage</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Reve</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Tatouage</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4073,54 +4071,54 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>5.5</v>
+        <v>300</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>45717</v>
+        <v>45740</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Virement Maman</t>
+          <t>Ternardier Project</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Reve</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t>Reve</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>400</v>
+        <v>70</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>45717</v>
+        <v>45747</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Alcool</t>
+          <t>Terreau +…</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Reve</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Alcool</t>
+          <t>Plante</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4129,44 +4127,44 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>26.7</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>45717</v>
+        <v>45777</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Virement Papa</t>
+          <t>Train Dijon</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Voyage</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>400</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>45716</v>
+        <v>45785</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Tram</t>
+          <t>Train Dijon (Allez + 2 *Retour)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4176,7 +4174,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tram</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4185,7 +4183,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>30</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="135">
@@ -4218,21 +4216,21 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>45715</v>
+        <v>45716</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Medoc pour tatouage</t>
+          <t>Tram</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Reve</t>
+          <t>Voyage</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tatouage</t>
+          <t>Tram</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4241,26 +4239,26 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>70.73</v>
+        <v>30</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>45715</v>
+        <v>45719</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Resto avec Emma</t>
+          <t>Tram</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Voyage</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Tram</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4269,26 +4267,26 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>11.2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>45715</v>
+        <v>45725</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>bouteille d'eau</t>
+          <t>Tram Charly</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Voyage</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Tram</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4297,110 +4295,110 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1.99</v>
+        <v>14</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>45714</v>
+        <v>45712</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Tatouage</t>
+          <t>Virement</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Reve</t>
+          <t xml:space="preserve">Banque </t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Tatouage</t>
+          <t>Livret_Bleu</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>45714</v>
+        <v>45730</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>fourniture en tout genre</t>
+          <t>Virement</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t xml:space="preserve">Banque </t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Fourniture</t>
+          <t>Livret_Bleu</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>6.38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>45714</v>
+        <v>45764</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nourrituresoir arrivé lyon </t>
+          <t>Virement</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t xml:space="preserve">Banque </t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Livret_Bleu</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>4.05</v>
+        <v>100</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>45713</v>
+        <v>45741</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Restaurant Mathieux</t>
+          <t>Virement</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t xml:space="preserve">Banque </t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Livret_Bleu</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4409,26 +4407,26 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>11</v>
+        <v>200</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>45713</v>
+        <v>45733</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Soggy</t>
+          <t>Virement</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t xml:space="preserve">Banque </t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Alcool</t>
+          <t>Livret_Bleu</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4437,26 +4435,26 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>9</v>
+        <v>350</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>45712</v>
+        <v>45803</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Achat divers déménagement Action</t>
+          <t>Virement</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t xml:space="preserve">Banque </t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Demenagement</t>
+          <t>Livret_Bleu</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4465,26 +4463,26 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>33.6</v>
+        <v>300</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>45712</v>
+        <v>45740</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Erreur de Compte</t>
+          <t>Virement</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Erreur de compte</t>
+          <t xml:space="preserve">Banque </t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Erreur de compte</t>
+          <t>Livret_Bleu</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4493,26 +4491,26 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>124.91</v>
+        <v>70</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>45712</v>
+        <v>45778</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Remboursement Pneu et Baterie</t>
+          <t>Virement Maman</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Poisse</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4521,54 +4519,54 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>246</v>
+        <v>400</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>45712</v>
+        <v>45809</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Parking Sainté</t>
+          <t>Virement Maman</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Voyage</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>20</v>
+        <v>400</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>45712</v>
+        <v>45717</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Virement</t>
+          <t>Virement Maman</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banque </t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Livret_Bleu</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4582,142 +4580,142 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>45711</v>
+        <v>45748</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Remplacement Pneu et baterie</t>
+          <t>Virement Maman</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Poisse</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>266</v>
+        <v>400</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>45711</v>
+        <v>45782</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Loyer</t>
+          <t>Virement Papa</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
           <t>Habitation</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Loyer</t>
-        </is>
-      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>137</v>
+        <v>400</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>45711</v>
+        <v>45813</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Essence</t>
+          <t>Virement Papa</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Voyage</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Voiture</t>
+          <t>Loyer</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>40</v>
+        <v>400</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>45710</v>
+        <v>45752</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Soggy</t>
+          <t>Virement Papa</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Alcool</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>6.2</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>45710</v>
+        <v>45717</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Exeptionnel Tram</t>
+          <t>Virement Papa</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Voyage</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Tram</t>
+          <t>Habitation</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Depense</t>
+          <t>Revenu</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1.6</v>
+        <v>400</v>
       </c>
     </row>
     <row r="154">
@@ -4750,21 +4748,21 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>45709</v>
+        <v>45780</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Restorant avec les P&amp;T guys </t>
+          <t>achat ordinateur a darius</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Poisse</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Ordinateur</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4773,26 +4771,26 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>16.9</v>
+        <v>257.9</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>45709</v>
+        <v>45797</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Caution</t>
+          <t>bar avec Emma</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Caution</t>
+          <t>Alcool</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4801,26 +4799,26 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>705</v>
+        <v>10</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>45707</v>
+        <v>45801</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t xml:space="preserve">biere avec mathieux </t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Essentiel</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Alcool</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4829,16 +4827,16 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>45706</v>
+        <v>45801</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Cannette,Chocolat Chaud, Repas Semaines</t>
+          <t>bonbon</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4857,44 +4855,44 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>20</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>45706</v>
+        <v>45715</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Caution Parents</t>
+          <t>bouteille d'eau</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>705</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>45703</v>
+        <v>45803</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Repas resto le midi et recherche appartement</t>
+          <t>course</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4918,21 +4916,21 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>45703</v>
+        <v>45801</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Déplacement Lyon Appartement</t>
+          <t>croissant</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Voyage</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -4941,16 +4939,16 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>45702</v>
+        <v>45765</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Restorant Margaux Titouan</t>
+          <t>feria lyon avec lau et guiguui</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4960,7 +4958,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Nourriture</t>
+          <t>Alcool</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4969,26 +4967,26 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>45698</v>
+        <v>45714</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>fourniture en tout genre</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Musique</t>
+          <t>Fourniture</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -4997,26 +4995,26 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>6.99</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>45698</v>
+        <v>45729</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Eau</t>
+          <t>fourniture en tout genre</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charge </t>
+          <t>Fourniture</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5025,26 +5023,26 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>19</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>45698</v>
+        <v>45731</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Loyer</t>
+          <t>fourniture en tout genre</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Habitation</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Loyer</t>
+          <t>Fourniture</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5053,63 +5051,175 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>229</v>
+        <v>48.27</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>45698</v>
+        <v>45724</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Fiver</t>
+          <t>fourniture en tout genre</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Essentiel</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Travail</t>
+          <t>Fourniture</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>6.99</v>
+        <v>19.96</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>45697</v>
+        <v>45801</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Compte au 09/02/2025</t>
+          <t>glace</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banque </t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Solde du mois</t>
+          <t>Nourriture</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Revenu</t>
+          <t>Depense</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>484.42</v>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>45757</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Essentiel</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Nourriture</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Depense</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>45736</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Essentiel</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Nourriture</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Depense</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>45801</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>resto Mathieux bk</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Loisir</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Nourriture</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Depense</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>45801</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>spotify</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Loisir</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Musique</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Depense</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>6.06</v>
       </c>
     </row>
   </sheetData>
